--- a/tables/TheGreatTable.xlsx
+++ b/tables/TheGreatTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anastasia/Desktop/greatuniter/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF556394-EEEB-D149-9DF9-7E54C7DA950D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B22BE827-A2CD-DA44-A5F5-FFA4A265E230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="460" windowWidth="25440" windowHeight="14580" xr2:uid="{96825E60-D260-2C40-A859-F3AC459E2BA5}"/>
+    <workbookView xWindow="80" yWindow="460" windowWidth="12640" windowHeight="14560" xr2:uid="{96825E60-D260-2C40-A859-F3AC459E2BA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
   <si>
     <t>The Great Table</t>
   </si>
@@ -47,39 +47,9 @@
     <t>класс объекта</t>
   </si>
   <si>
-    <t>opm</t>
-  </si>
-  <si>
-    <t>osa</t>
-  </si>
-  <si>
     <t>вызов объекта в приложении-функции</t>
   </si>
   <si>
-    <t>fpga</t>
-  </si>
-  <si>
-    <t>switch</t>
-  </si>
-  <si>
-    <t>atten</t>
-  </si>
-  <si>
-    <t>app.callingApp.appDeviceOPM.opm</t>
-  </si>
-  <si>
-    <t>app.callingApp.appDeviceOSA.osa</t>
-  </si>
-  <si>
-    <t>app.callingApp.appDeviceFPGA.fpga</t>
-  </si>
-  <si>
-    <t>app.callingApp.appDeviceSWITCH.switch</t>
-  </si>
-  <si>
-    <t>app.callingApp.appDeviceATTEN.atten</t>
-  </si>
-  <si>
     <t>appTestEDFA.mlapp</t>
   </si>
   <si>
@@ -113,36 +83,6 @@
     <t>Устройства</t>
   </si>
   <si>
-    <t>FPGA_Attenuator</t>
-  </si>
-  <si>
-    <t>FPGA_Photodiode</t>
-  </si>
-  <si>
-    <t>FPGA_LaserDiode</t>
-  </si>
-  <si>
-    <t>FPGA_LoadDriver</t>
-  </si>
-  <si>
-    <t>FPGA_Parameter</t>
-  </si>
-  <si>
-    <t>FPGA_Transceiver</t>
-  </si>
-  <si>
-    <t>OSA</t>
-  </si>
-  <si>
-    <t>FPGA</t>
-  </si>
-  <si>
-    <t>SWITCH</t>
-  </si>
-  <si>
-    <t>ATTEN</t>
-  </si>
-  <si>
     <t>FPGA_attenuator</t>
   </si>
   <si>
@@ -161,25 +101,73 @@
     <t>FPGA_transceiver</t>
   </si>
   <si>
-    <t>appAddDeviceOSA_Yokogawa.mlapp</t>
-  </si>
-  <si>
-    <t>appAddDeviceFPGA.mlapp</t>
-  </si>
-  <si>
-    <t>appAddDeviceSWITCH_OsaEdfa.mlapp</t>
-  </si>
-  <si>
-    <t>appAddDeviceATTEN_NiMyDaq.mlapp</t>
-  </si>
-  <si>
-    <t>Device_OPMrubin</t>
-  </si>
-  <si>
     <t>appAddDevice_OPMrubin.mlapp</t>
   </si>
   <si>
     <t>приложение для создания таблиц</t>
+  </si>
+  <si>
+    <t>Device_OPMrubin.m</t>
+  </si>
+  <si>
+    <t>appAddDevice_OSAyokogawa.mlapp</t>
+  </si>
+  <si>
+    <t>appAddDevice_FPGA.mlapp</t>
+  </si>
+  <si>
+    <t>appAddDevice_SWITCHosaEdfa.mlapp</t>
+  </si>
+  <si>
+    <t>appAddDevice_ATTENniMyDaq.mlapp</t>
+  </si>
+  <si>
+    <t>Device_OSAyokogawa.m</t>
+  </si>
+  <si>
+    <t>Device_FPGA.m</t>
+  </si>
+  <si>
+    <t>Device_SWITCHosaEdfa.m</t>
+  </si>
+  <si>
+    <t>mainObj</t>
+  </si>
+  <si>
+    <t>app.callingApp.appAddDevice_OPMrubin.mainObj</t>
+  </si>
+  <si>
+    <t>app.callingApp.appAddDevice_OSAyokogawa.mainObj</t>
+  </si>
+  <si>
+    <t>Device_ATTENniMyDaq.m</t>
+  </si>
+  <si>
+    <t>app.callingApp.appAddDevice_ATTENniMyDaq.mainObj</t>
+  </si>
+  <si>
+    <t>app.callingApp.appAddDevice_SWITCHosaEdfa.mainObj</t>
+  </si>
+  <si>
+    <t>app.callingApp.appAddDevice_FPGA.mainObj</t>
+  </si>
+  <si>
+    <t>FPGA_Attenuator.m</t>
+  </si>
+  <si>
+    <t>FPGA_Photodiode.m</t>
+  </si>
+  <si>
+    <t>FPGA_LaserDiode.m</t>
+  </si>
+  <si>
+    <t>FPGA_LoadDriver.m</t>
+  </si>
+  <si>
+    <t>FPGA_Parameter.m</t>
+  </si>
+  <si>
+    <t>FPGA_Transceiver.m</t>
   </si>
 </sst>
 </file>
@@ -308,12 +296,22 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -324,16 +322,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -660,257 +648,257 @@
   <cols>
     <col min="1" max="1" width="41.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.6640625" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" customWidth="1"/>
-    <col min="4" max="4" width="41.83203125" customWidth="1"/>
+    <col min="3" max="3" width="27.83203125" customWidth="1"/>
+    <col min="4" max="4" width="54.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:4" ht="40" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="7"/>
+    </row>
+    <row r="5" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="7"/>
+    </row>
+    <row r="11" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="9"/>
-    </row>
-    <row r="5" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="9"/>
-    </row>
-    <row r="11" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="C18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A19" s="8"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="10"/>
+    </row>
+    <row r="20" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+    </row>
+    <row r="22" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="6"/>
-    </row>
-    <row r="20" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-    </row>
-    <row r="22" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-    </row>
-    <row r="23" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-    </row>
-    <row r="24" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/tables/TheGreatTable.xlsx
+++ b/tables/TheGreatTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10313"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23001"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anastasia/Desktop/greatuniter/tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\greatuniter\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B22BE827-A2CD-DA44-A5F5-FFA4A265E230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{350F1AF0-5B37-4DE9-B00B-1D02B14B6C6F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="460" windowWidth="12640" windowHeight="14560" xr2:uid="{96825E60-D260-2C40-A859-F3AC459E2BA5}"/>
+    <workbookView xWindow="-16890" yWindow="1065" windowWidth="14400" windowHeight="10755" xr2:uid="{96825E60-D260-2C40-A859-F3AC459E2BA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,6 @@
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -644,15 +642,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F216D979-E3DE-124E-89F3-7E2F40A075E3}">
   <dimension ref="A1:D24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="41.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.6640625" customWidth="1"/>
-    <col min="3" max="3" width="27.83203125" customWidth="1"/>
+    <col min="1" max="1" width="41.875" customWidth="1"/>
+    <col min="2" max="2" width="20.625" customWidth="1"/>
+    <col min="3" max="3" width="27.875" customWidth="1"/>
     <col min="4" max="4" width="54.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -660,13 +658,13 @@
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -680,7 +678,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
@@ -688,7 +686,7 @@
       <c r="C4" s="6"/>
       <c r="D4" s="7"/>
     </row>
-    <row r="5" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
@@ -702,7 +700,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>25</v>
       </c>
@@ -716,7 +714,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
@@ -730,7 +728,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>27</v>
       </c>
@@ -744,7 +742,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>28</v>
       </c>
@@ -758,7 +756,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
@@ -766,7 +764,7 @@
       <c r="C10" s="6"/>
       <c r="D10" s="7"/>
     </row>
-    <row r="11" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -778,7 +776,7 @@
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
@@ -790,7 +788,7 @@
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
@@ -802,7 +800,7 @@
       </c>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
@@ -814,7 +812,7 @@
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
@@ -826,7 +824,7 @@
       </c>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
@@ -838,7 +836,7 @@
       </c>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>5</v>
       </c>
@@ -850,7 +848,7 @@
       </c>
       <c r="D17" s="1"/>
     </row>
-    <row r="18" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>6</v>
       </c>
@@ -862,37 +860,37 @@
       </c>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="10"/>
     </row>
-    <row r="20" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
     </row>
-    <row r="21" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
     </row>
-    <row r="24" spans="1:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>23</v>
       </c>

--- a/tables/TheGreatTable.xlsx
+++ b/tables/TheGreatTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\greatuniter\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{350F1AF0-5B37-4DE9-B00B-1D02B14B6C6F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83D176A-59B7-4DAE-BABA-C2148CC949A5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16890" yWindow="1065" windowWidth="14400" windowHeight="10755" xr2:uid="{96825E60-D260-2C40-A859-F3AC459E2BA5}"/>
+    <workbookView xWindow="-18240" yWindow="930" windowWidth="14400" windowHeight="10755" xr2:uid="{96825E60-D260-2C40-A859-F3AC459E2BA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>

--- a/tables/TheGreatTable.xlsx
+++ b/tables/TheGreatTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\greatuniter\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83D176A-59B7-4DAE-BABA-C2148CC949A5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE0E7F8-4881-4E9B-8684-9717FD732C16}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-18240" yWindow="930" windowWidth="14400" windowHeight="10755" xr2:uid="{96825E60-D260-2C40-A859-F3AC459E2BA5}"/>
   </bookViews>

--- a/tables/TheGreatTable.xlsx
+++ b/tables/TheGreatTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\greatuniter\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE0E7F8-4881-4E9B-8684-9717FD732C16}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7D19A0-C2F0-42AB-95A3-C61EAAB6CB52}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18240" yWindow="930" windowWidth="14400" windowHeight="10755" xr2:uid="{96825E60-D260-2C40-A859-F3AC459E2BA5}"/>
+    <workbookView xWindow="-16365" yWindow="1065" windowWidth="14400" windowHeight="10755" xr2:uid="{96825E60-D260-2C40-A859-F3AC459E2BA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>

--- a/tables/TheGreatTable.xlsx
+++ b/tables/TheGreatTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\greatuniter\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7D19A0-C2F0-42AB-95A3-C61EAAB6CB52}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C221DD-18F2-4A0B-862D-BFA000B7D3C2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16365" yWindow="1065" windowWidth="14400" windowHeight="10755" xr2:uid="{96825E60-D260-2C40-A859-F3AC459E2BA5}"/>
+    <workbookView xWindow="-16155" yWindow="1665" windowWidth="14400" windowHeight="10755" xr2:uid="{96825E60-D260-2C40-A859-F3AC459E2BA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="47">
   <si>
     <t>The Great Table</t>
   </si>
@@ -166,13 +166,19 @@
   </si>
   <si>
     <t>FPGA_Transceiver.m</t>
+  </si>
+  <si>
+    <t>FPGA_Component</t>
+  </si>
+  <si>
+    <t>superclass</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -213,8 +219,16 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -224,6 +238,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF5F5FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -292,13 +312,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -318,6 +344,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -641,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F216D979-E3DE-124E-89F3-7E2F40A075E3}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.875" customWidth="1"/>
@@ -651,18 +680,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
     </row>
     <row r="3" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -679,12 +708,12 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="9"/>
     </row>
     <row r="5" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -696,7 +725,7 @@
       <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -710,7 +739,7 @@
       <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="3" t="s">
         <v>34</v>
       </c>
     </row>
@@ -724,7 +753,7 @@
       <c r="C7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="3" t="s">
         <v>38</v>
       </c>
     </row>
@@ -738,7 +767,7 @@
       <c r="C8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="3" t="s">
         <v>37</v>
       </c>
     </row>
@@ -752,105 +781,103 @@
       <c r="C9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="7"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="9"/>
     </row>
     <row r="11" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="1"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D14" s="1"/>
     </row>
     <row r="15" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" s="1"/>
     </row>
     <row r="16" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D16" s="1"/>
     </row>
     <row r="17" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="D17" s="1"/>
     </row>
     <row r="18" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
@@ -861,16 +888,22 @@
       <c r="D18" s="1"/>
     </row>
     <row r="19" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="10"/>
+      <c r="A19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="1"/>
     </row>
     <row r="20" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="12"/>
     </row>
     <row r="21" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
@@ -891,20 +924,27 @@
       <c r="D23" s="1"/>
     </row>
     <row r="24" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
+    </row>
+    <row r="25" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:D2"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A20:D20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>